--- a/data/dividends_info_20260830.xlsx
+++ b/data/dividends_info_20260830.xlsx
@@ -2059,7 +2059,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2178,7 +2178,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2195,7 +2195,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2212,7 +2212,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2229,7 +2229,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2246,7 +2246,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2263,7 +2263,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2365,7 +2365,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2450,7 +2450,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2467,7 +2467,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2477,14 +2477,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2552,7 +2552,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2562,14 +2562,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2579,14 +2579,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>I GRANDI VIAGGI S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2613,14 +2613,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>I GRANDI VIAGGI S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2630,14 +2630,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2654,7 +2654,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2664,14 +2664,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2688,7 +2688,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2698,14 +2698,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MB Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2722,7 +2722,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2732,14 +2732,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>MB Annual Report</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2749,14 +2749,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2766,14 +2766,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2790,7 +2790,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2800,14 +2800,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2817,14 +2817,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2834,14 +2834,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2858,7 +2858,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2875,7 +2875,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2885,14 +2885,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2902,14 +2902,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3198,7 +3198,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3215,7 +3215,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3232,7 +3232,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3334,7 +3334,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3351,7 +3351,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3368,7 +3368,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3385,7 +3385,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3419,7 +3419,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3436,7 +3436,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3470,7 +3470,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>JUVENTUS F.C. S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3504,7 +3504,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3521,7 +3521,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3538,7 +3538,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3572,7 +3572,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3589,7 +3589,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3623,7 +3623,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3640,7 +3640,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3657,7 +3657,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3667,14 +3667,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3691,7 +3691,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3708,7 +3708,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3725,7 +3725,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3742,7 +3742,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3759,7 +3759,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3769,14 +3769,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3786,14 +3786,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3810,7 +3810,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3827,7 +3827,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3844,7 +3844,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3861,7 +3861,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3878,7 +3878,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3912,7 +3912,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3963,7 +3963,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3980,7 +3980,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3997,7 +3997,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4014,7 +4014,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Guidotti Ships S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4031,7 +4031,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4048,7 +4048,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4082,7 +4082,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4116,7 +4116,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4126,14 +4126,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Guidotti Ships S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4150,7 +4150,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4167,7 +4167,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4177,14 +4177,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4194,14 +4194,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4211,14 +4211,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4235,7 +4235,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4252,7 +4252,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4269,7 +4269,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4279,14 +4279,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4296,14 +4296,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4320,7 +4320,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4337,7 +4337,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4354,7 +4354,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4371,7 +4371,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4388,7 +4388,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4405,7 +4405,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4422,7 +4422,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4439,7 +4439,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4456,7 +4456,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4466,14 +4466,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4483,14 +4483,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4507,7 +4507,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4524,7 +4524,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4541,7 +4541,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4551,14 +4551,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4575,7 +4575,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4585,14 +4585,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4609,7 +4609,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4619,14 +4619,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4636,14 +4636,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>Gens Aurea S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4660,7 +4660,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4677,7 +4677,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4694,7 +4694,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4711,7 +4711,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4728,7 +4728,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4745,7 +4745,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4762,7 +4762,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4779,7 +4779,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4796,7 +4796,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4813,7 +4813,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4830,7 +4830,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4847,7 +4847,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4864,7 +4864,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4881,7 +4881,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4898,7 +4898,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4932,7 +4932,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4949,7 +4949,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4959,14 +4959,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4983,7 +4983,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ETI S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5000,7 +5000,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5017,7 +5017,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5034,7 +5034,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5051,7 +5051,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5068,7 +5068,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5085,7 +5085,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5102,7 +5102,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5119,7 +5119,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5136,7 +5136,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5153,7 +5153,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5170,7 +5170,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5187,7 +5187,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5204,7 +5204,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5221,7 +5221,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5238,7 +5238,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5248,14 +5248,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5272,7 +5272,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5289,7 +5289,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5306,7 +5306,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5323,7 +5323,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5340,7 +5340,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>EPH INVEST S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5374,7 +5374,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5391,7 +5391,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5401,14 +5401,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5425,7 +5425,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5442,7 +5442,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5459,7 +5459,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5469,14 +5469,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5493,7 +5493,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5510,7 +5510,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5527,7 +5527,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>ETI S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5544,7 +5544,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5561,7 +5561,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5571,14 +5571,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5595,7 +5595,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5612,7 +5612,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5629,7 +5629,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>EPH INVEST S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5646,7 +5646,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5684,1047 +5684,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ATON Green Storage S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Adventure S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Arterra Bioscience S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BORGOSESIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Bellini Nautica S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>COFLE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Copernico SIM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Datrix S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ENA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>EPH INVEST S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ETI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>EUKEDOS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Energy S.p.A.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Energy Time S.p.A.</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>ErreDue S.p.A.</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>FIDIA S.p.A</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>First Capital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>GEL S.p.A.</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>GPI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>GREEN OLEO S.p.A</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Gambero Rosso S.p.A.</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Gens Aurea S.p.A.</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Grifal S.p.A.</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>ISCC FINTECH S.p.A.</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>International Care Company S.p.A.</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Lemon Sistemi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Magis S.p.A.</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Monnalisa S.p.A.</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Novamarine S.p.A.</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>OPS Italia S.p.A.</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Otofarma S.p.A.</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>PLANETEL S.p.A.</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Racing Force S.p.A.</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Reti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Rocket Sharing Company S.p.A.</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>SIAV S.p.A.</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>SOGES GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Seri Industrial S.p.A.</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>TESSELLIS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Telesia S.p.A.</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>UCapital24 S.p.A.</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Vimi Fasteners S.p.A.</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>iVision Tech S.p.A.</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>